--- a/results/Int All Data -0.0/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_8_permute.xlsx
@@ -440,757 +440,757 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8969015588244832</v>
+        <v>0.8809366417297988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8911137774740009</v>
+        <v>0.8804823899480891</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8985756300529586</v>
+        <v>0.8800383656913932</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8988971734613187</v>
+        <v>0.8769454124561277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8988971734613187</v>
+        <v>0.8776548534595228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8988971734613187</v>
+        <v>0.8789410270929632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8902155014355952</v>
+        <v>0.8782315860895682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8882198867987597</v>
+        <v>0.8779100426812081</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8875104457953646</v>
+        <v>0.8804823899480891</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8871889023870045</v>
+        <v>0.8977130256261865</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8884087218337703</v>
+        <v>0.8922467876840643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8884087218337703</v>
+        <v>0.8916037008673441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.888153532612085</v>
+        <v>0.8880667233753825</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.888153532612085</v>
+        <v>0.8923692685324001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8849942251901446</v>
+        <v>0.8926908119407602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8891742894988264</v>
+        <v>0.9013622564414698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8898173763155466</v>
+        <v>0.9011070672197845</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8914148658323334</v>
+        <v>0.8984122391045677</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8885873293437672</v>
+        <v>0.8959062460243614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8860149820768861</v>
+        <v>0.8955744750909875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8883321401220817</v>
+        <v>0.8957633101259981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.887821761678711</v>
+        <v>0.8958398918376866</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8862803988235852</v>
+        <v>0.8747609627842816</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8911137774740009</v>
+        <v>0.8699939383205406</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8904706906572806</v>
+        <v>0.8661354174202192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8907922340656408</v>
+        <v>0.8675542994270091</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8907922340656408</v>
+        <v>0.8477765111168207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8970649497728741</v>
+        <v>0.8477765111168207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8987390210013495</v>
+        <v>0.849573063193632</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8936963522658956</v>
+        <v>0.8405034935728737</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8978764165745774</v>
+        <v>0.8449592021532681</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8949059441876477</v>
+        <v>0.845622744020016</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9054914325769122</v>
+        <v>0.8382629172393665</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9041491322818107</v>
+        <v>0.8308112921854225</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.904792219098531</v>
+        <v>0.8302141045053495</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8896337797689577</v>
+        <v>0.8366449726725521</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8918743561024649</v>
+        <v>0.8301477503186747</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8908331441656959</v>
+        <v>0.8298262069103146</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8908331441656959</v>
+        <v>0.8116411685321506</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8876074825570808</v>
+        <v>0.8106765383070702</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8872859391487207</v>
+        <v>0.8071395608151088</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.894446703369346</v>
+        <v>0.8071395608151088</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8951561443727409</v>
+        <v>0.8071395608151088</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8844993127602094</v>
+        <v>0.8068180174067487</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8848208561685695</v>
+        <v>0.8097119080819899</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8832897208384576</v>
+        <v>0.8183935801077133</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.880140640941531</v>
+        <v>0.8294944359769407</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8789105939697515</v>
+        <v>0.8298159793853008</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8717448407125342</v>
+        <v>0.835711025022513</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8782981897280726</v>
+        <v>0.8643897535166472</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.869948288635723</v>
+        <v>0.8571319525343059</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8556676702945278</v>
+        <v>0.8512982720471762</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8481955901905562</v>
+        <v>0.8492158481736385</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8485171335989163</v>
+        <v>0.8271518338451254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8467869357087799</v>
+        <v>0.7940483287974676</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8490938662289619</v>
+        <v>0.7986928724128727</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8467512640971465</v>
+        <v>0.8018776239214327</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8346653229528112</v>
+        <v>0.7963807034042691</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8306077394924654</v>
+        <v>0.7989428231461364</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8202519962382664</v>
+        <v>0.800606666849598</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.823610366220231</v>
+        <v>0.8034444308631782</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8242534530369513</v>
+        <v>0.7978609505611418</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8192975935381999</v>
+        <v>0.7805639606963697</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.81490823914448</v>
+        <v>0.7717902409455222</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.81490823914448</v>
+        <v>0.7623073296431093</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7958708238645575</v>
+        <v>0.7639150466849099</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7901391691757362</v>
+        <v>0.7736277031223886</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7360076232479127</v>
+        <v>0.7739697015807763</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7288009598906403</v>
+        <v>0.7760775695409339</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7345223870544478</v>
+        <v>0.7796706736945562</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7249526665153325</v>
+        <v>0.7887554598769204</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7209716647666753</v>
+        <v>0.7816253782313366</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7146632774478084</v>
+        <v>0.7840752446498819</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7128564978459835</v>
+        <v>0.7721524450021079</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6971008708363372</v>
+        <v>0.7835289451430481</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.70417482582026</v>
+        <v>0.7832737559213628</v>
       </c>
     </row>
     <row r="78">
@@ -1200,177 +1200,177 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7256621075187276</v>
+        <v>0.7746736546439199</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7268258003038324</v>
+        <v>0.7670229670299518</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.736094432484615</v>
+        <v>0.7670229670299518</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7335016301677064</v>
+        <v>0.7679875972550321</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7516305418842094</v>
+        <v>0.7710653339286917</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7432040590801714</v>
+        <v>0.7710755614537055</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7235899111702035</v>
+        <v>0.7341596840942031</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7392894115181887</v>
+        <v>0.735032516045989</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7386463247014685</v>
+        <v>0.7305002257539057</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7348643855128355</v>
+        <v>0.7343587466542273</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7134995846627037</v>
+        <v>0.7350784151826362</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6276577221555631</v>
+        <v>0.7350784151826362</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6248301856669968</v>
+        <v>0.7327305745623991</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6163373486762839</v>
+        <v>0.7378498250095415</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5803244869399495</v>
+        <v>0.7382377226045764</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5845606779102922</v>
+        <v>0.7345680367392655</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5835399210235508</v>
+        <v>0.7227934114782765</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.56726368804552</v>
+        <v>0.7227270572916018</v>
       </c>
     </row>
     <row r="96">
@@ -1380,607 +1380,607 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.559587556344932</v>
+        <v>0.6997545393996693</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5579798393031313</v>
+        <v>0.7144841710341525</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5608073757916977</v>
+        <v>0.7133970599607362</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5529678531427189</v>
+        <v>0.7201547100247208</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5529678531427189</v>
+        <v>0.7182918037612347</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.558821988679876</v>
+        <v>0.6925072153941714</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.558821988679876</v>
+        <v>0.6936811357042898</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5682028741839806</v>
+        <v>0.6982031984713593</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5459190927935861</v>
+        <v>0.6552797726994929</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5316943516622222</v>
+        <v>0.6496144721973462</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5230229071615126</v>
+        <v>0.6490938662289618</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5476592687569066</v>
+        <v>0.6401926765931865</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5679110155433436</v>
+        <v>0.6404019666782246</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5691869616517702</v>
+        <v>0.6400804232698645</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5411820025493977</v>
+        <v>0.6186033690964107</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5324798754736466</v>
+        <v>0.6134534360742269</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5038265910661321</v>
+        <v>0.6128103492575067</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4753671307302203</v>
+        <v>0.6080281082321598</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4865650233611639</v>
+        <v>0.5762157658545347</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4889792181680757</v>
+        <v>0.5607357831166012</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.462147929923992</v>
+        <v>0.5564536930096113</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4694311749929529</v>
+        <v>0.5564536930096113</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4710388920347536</v>
+        <v>0.5445004602386256</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5014383392494992</v>
+        <v>0.5175878506980909</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4306064922333173</v>
+        <v>0.5217679150067726</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4306064922333173</v>
+        <v>0.5217679150067726</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4580047844860918</v>
+        <v>0.5287907323656266</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4682891845170238</v>
+        <v>0.5350327654978185</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.471780262872338</v>
+        <v>0.5390698939081369</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4681871587187156</v>
+        <v>0.5355329164161755</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4678094886486945</v>
+        <v>0.5195986818965324</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4542126177724451</v>
+        <v>0.5178530179929605</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4540389992990403</v>
+        <v>0.5180061814163376</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4647674235866683</v>
+        <v>0.503863260485084</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4685443737387092</v>
+        <v>0.4964370795177597</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4504561226704317</v>
+        <v>0.4964370795177597</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4504561226704317</v>
+        <v>0.4971260654711272</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4586683263528397</v>
+        <v>0.4980906956962076</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.457060609311039</v>
+        <v>0.5009182321847739</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.457060609311039</v>
+        <v>0.4942219472708723</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5008573659383505</v>
+        <v>0.5034496693515998</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4964884665946582</v>
+        <v>0.5028065825348796</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4996477740165985</v>
+        <v>0.5197820289912917</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4996477740165985</v>
+        <v>0.5170872008760748</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4996477740165985</v>
+        <v>0.5233803716333357</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5003572150199935</v>
+        <v>0.5263406164952517</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5016229336034065</v>
+        <v>0.5081246460902167</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5016229336034065</v>
+        <v>0.4930071168606986</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5023885012684626</v>
+        <v>0.4926192192656637</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5033531314935429</v>
+        <v>0.4928080543006743</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5003928866316271</v>
+        <v>0.4368485253655093</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5003928866316271</v>
+        <v>0.4652880295550528</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5018424512134584</v>
+        <v>0.4772312842528544</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5024294113685177</v>
+        <v>0.4757001489227423</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5016077170418006</v>
+        <v>0.4755674405493927</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.4996121024049651</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.5002551892216853</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.4996121024049651</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4996121024049651</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4996121024049651</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4996121024049651</v>
       </c>
     </row>
   </sheetData>
